--- a/dev-docs/task-260902-报价与核价建表与导入方案新规范/报价 - 数据导入与表格建表.xlsx
+++ b/dev-docs/task-260902-报价与核价建表与导入方案新规范/报价 - 数据导入与表格建表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\dev-docs\task-260902-报价与核价建表与导入方案新规范\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597CD827-15C1-428E-9532-301720EEF0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F320D2E-ED59-47A7-A433-69B997FFF9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="840" windowWidth="28395" windowHeight="14640" tabRatio="912" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="物料" sheetId="1" r:id="rId1"/>
@@ -1132,6 +1132,9 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
+      <c r="G2" s="5">
+        <v>33</v>
+      </c>
       <c r="I2" s="41" t="s">
         <v>128</v>
       </c>
@@ -1145,6 +1148,9 @@
       </c>
       <c r="C3" t="s">
         <v>10</v>
+      </c>
+      <c r="G3" s="5">
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:9">
